--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129009110</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129009118</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129007438</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129007415</v>
       </c>
       <c r="B5" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1086,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R6" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>57717</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R7" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129009113</v>
       </c>
       <c r="B9" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1086,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R6" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R7" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129009118</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129007438</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129007415</v>
       </c>
       <c r="B5" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,42 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R6" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1183,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R7" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1086,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R6" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R7" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129009110</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129009118</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129007438</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129007415</v>
       </c>
       <c r="B5" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,42 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R6" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1183,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R7" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129009113</v>
       </c>
       <c r="B9" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129009110</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>129009118</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129007438</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129007415</v>
       </c>
       <c r="B5" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129007426</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129009113</v>
       </c>
       <c r="B9" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1086,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R6" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R7" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,42 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R6" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1183,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R7" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,34 +1086,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R6" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,42 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R7" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -1075,10 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129007426</v>
+        <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1086,42 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440767</v>
+        <v>440854</v>
       </c>
       <c r="R6" t="n">
-        <v>6781816</v>
+        <v>6781849</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129007446</v>
+        <v>129007426</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1183,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skrådajkarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440854</v>
+        <v>440767</v>
       </c>
       <c r="R7" t="n">
-        <v>6781849</v>
+        <v>6781816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>129009118</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>129007438</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>129007415</v>
       </c>
       <c r="B5" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>129007446</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129009114</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39267-2021 artfynd.xlsx
+++ b/artfynd/A 39267-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328521</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007435</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007437</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007439</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007441</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007442</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007444</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007445</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007446</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2074,6 +2144,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129009118</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2260,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328525</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328548</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007415</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2498,6 +2588,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007425</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007426</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2715,6 +2815,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328523</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2820,6 +2925,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007419</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,6 +3035,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129009110</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129009113</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3134,6 +3254,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007431</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3236,6 +3361,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129009114</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3352,6 +3482,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134328524</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3449,8 +3584,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129007429</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>